--- a/data/trans_orig/P33B_R3-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R3-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72088</t>
+          <t>79552</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>63835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91162</t>
+          <t>96561</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68015</t>
+          <t>76488</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57707</t>
+          <t>64296</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81877</t>
+          <t>90965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140104</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122175</t>
+          <t>136212</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>161315</t>
+          <t>179466</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>433124</t>
+          <t>471066</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414050</t>
+          <t>454057</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>446892</t>
+          <t>486783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>379452</t>
+          <t>411923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365590</t>
+          <t>397446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389760</t>
+          <t>424115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>812575</t>
+          <t>882989</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>791364</t>
+          <t>859563</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>830504</t>
+          <t>902817</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,89%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59122</t>
+          <t>62074</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46242</t>
+          <t>48512</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74925</t>
+          <t>76266</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58997</t>
+          <t>68529</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48293</t>
+          <t>56489</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71006</t>
+          <t>82185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118119</t>
+          <t>130603</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101216</t>
+          <t>112362</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139105</t>
+          <t>151939</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>392122</t>
+          <t>420150</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>376319</t>
+          <t>405958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405002</t>
+          <t>433712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>323583</t>
+          <t>354614</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>311574</t>
+          <t>340958</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334287</t>
+          <t>366654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>715705</t>
+          <t>774764</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>694719</t>
+          <t>753428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>732608</t>
+          <t>793005</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,59%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88025</t>
+          <t>94556</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>76992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>147499</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47156</t>
+          <t>53187</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>42800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57021</t>
+          <t>63856</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>135181</t>
+          <t>147742</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63269</t>
+          <t>128112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196207</t>
+          <t>168165</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>580239</t>
+          <t>377056</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520765</t>
+          <t>359454</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634393</t>
+          <t>394620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>119755</t>
+          <t>134310</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>109890</t>
+          <t>123641</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>128207</t>
+          <t>144697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>699994</t>
+          <t>511367</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>638968</t>
+          <t>490944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>771906</t>
+          <t>530997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>80,56%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>172033</t>
+          <t>191019</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149382</t>
+          <t>165635</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>197979</t>
+          <t>218017</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>157505</t>
+          <t>176234</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90340</t>
+          <t>154580</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205858</t>
+          <t>195621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>329539</t>
+          <t>367253</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>231984</t>
+          <t>335599</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379659</t>
+          <t>400093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>862786</t>
+          <t>940824</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>836840</t>
+          <t>913826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>885437</t>
+          <t>966208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>820589</t>
+          <t>684977</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>772236</t>
+          <t>665590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887754</t>
+          <t>706631</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1683373</t>
+          <t>1625801</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1633253</t>
+          <t>1592961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1780928</t>
+          <t>1657455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>83,16%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>90443</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67725</t>
+          <t>73283</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104332</t>
+          <t>109634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>218939</t>
+          <t>240800</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>165515</t>
+          <t>218040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>255653</t>
+          <t>261927</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>302826</t>
+          <t>331242</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>245739</t>
+          <t>304094</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335901</t>
+          <t>360172</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,78%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>476439</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>369684</t>
+          <t>457248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>406291</t>
+          <t>493599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>620057</t>
+          <t>589327</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>583343</t>
+          <t>568200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>673481</t>
+          <t>612087</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1010186</t>
+          <t>1065767</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>977111</t>
+          <t>1036837</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1067273</t>
+          <t>1092915</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>78,23%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>170735</t>
+          <t>191926</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152895</t>
+          <t>172581</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>190429</t>
+          <t>212549</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>185157</t>
+          <t>206854</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>163830</t>
+          <t>182566</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>207674</t>
+          <t>231865</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>226085</t>
+          <t>222299</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210824</t>
+          <t>206484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234776</t>
+          <t>230214</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>590636</t>
+          <t>652355</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>570942</t>
+          <t>631732</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>608476</t>
+          <t>671700</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>816721</t>
+          <t>874655</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>794204</t>
+          <t>849644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>838048</t>
+          <t>898943</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>489578</t>
+          <t>532572</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>390862</t>
+          <t>489879</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>545692</t>
+          <t>579425</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>721347</t>
+          <t>807163</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>582924</t>
+          <t>766214</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>783803</t>
+          <t>847816</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1210925</t>
+          <t>1339736</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1033101</t>
+          <t>1282416</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1304774</t>
+          <t>1409615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2884484</t>
+          <t>2907834</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2828370</t>
+          <t>2860981</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2983200</t>
+          <t>2950527</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2854071</t>
+          <t>2827507</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2791615</t>
+          <t>2786854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2992494</t>
+          <t>2868456</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5738555</t>
+          <t>5735341</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5644706</t>
+          <t>5665462</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5916379</t>
+          <t>5792661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>81,87%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
